--- a/data/trans_dic/IP31KM01_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM01_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90,39; 97,29</t>
+          <t>86,5; 96,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74,03; 94,78</t>
+          <t>90,47; 97,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,22; 95,11</t>
+          <t>90,1; 95,8</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,0; 97,02</t>
+          <t>89,7; 95,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,7; 95,67</t>
+          <t>91,4; 97,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,36; 95,85</t>
+          <t>91,19; 95,62</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,69; 93,18</t>
+          <t>79,35; 89,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,96; 90,19</t>
+          <t>80,82; 90,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,59; 90,55</t>
+          <t>81,84; 89,19</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,99%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,63; 91,69</t>
+          <t>83,1; 92,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,34; 92,86</t>
+          <t>82,97; 91,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,0; 90,97</t>
+          <t>84,54; 90,7</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,95; 92,91</t>
+          <t>87,51; 91,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,8; 91,59</t>
+          <t>88,58; 92,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,57; 91,71</t>
+          <t>88,84; 91,77</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>178</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>108267</t>
+          <t>113249</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>121698</t>
+          <t>112352</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229966</t>
+          <t>225601</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>103274; 111152</t>
+          <t>106309; 118038</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>101290; 129679</t>
+          <t>107292; 115295</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>211452; 238785</t>
+          <t>217581; 231353</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>255</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>176157</t>
+          <t>215026</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>230670</t>
+          <t>171225</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>406827</t>
+          <t>386249</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>169359; 180566</t>
+          <t>207417; 221430</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>222029; 236794</t>
+          <t>165055; 175240</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>396153; 415639</t>
+          <t>375567; 393775</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>191</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>166861</t>
+          <t>142520</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>157397</t>
+          <t>133466</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>324258</t>
+          <t>275986</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>157542; 175404</t>
+          <t>132140; 149733</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>146395; 165122</t>
+          <t>125296; 139797</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>310419; 336231</t>
+          <t>263156; 286800</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>207</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>144563</t>
+          <t>146770</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>157560</t>
+          <t>143730</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302123</t>
+          <t>290500</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>135934; 150854</t>
+          <t>138085; 153978</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>147766; 164655</t>
+          <t>136045; 150160</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>290558; 310954</t>
+          <t>279108; 299444</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>831</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>595849</t>
+          <t>617565</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>667324</t>
+          <t>560772</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1263174</t>
+          <t>1178336</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>580984; 606819</t>
+          <t>601064; 631556</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646433; 682126</t>
+          <t>547624; 572223</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1238024; 1281985</t>
+          <t>1159390; 1197619</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM01_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM01_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman una fruta o un zumo natural todos los días (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>92,15%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>93,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>86,5; 96,05</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>90,47; 97,21</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>90,1; 95,8</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>92,99%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>94,81%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>93,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>89,7; 95,76</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>91,4; 97,04</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>91,19; 95,62</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>85,59%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>86,09%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>85,83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>79,35; 89,92</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>80,82; 90,17</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>81,84; 89,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>88,33%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>87,65%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>87,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>83,1; 92,67</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>82,97; 91,57</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>84,54; 90,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>89,92%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>90,71%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>90,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>87,51; 91,95</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>88,58; 92,56</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>88,84; 91,77</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9215034064650734</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9473357146367837</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9341896491749629</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>113249</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>112352</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>225601</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.8650343954815262</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.9046714156140184</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.9009773184499609</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>106309; 118038</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>107292; 115295</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>217581; 231353</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9604732622050653</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9721492189142401</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9580070221373744</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9298779585643965</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9481237563071142</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.937878913205794</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>215026</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>171225</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>386249</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8969730403930881</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9139631824575049</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9119403576718165</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>207417; 221430</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>165055; 175240</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>375567; 393775</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9575706318914206</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9703595014401971</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9561521163186837</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.85586235041415</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8608609712567828</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8582724048850913</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>142520</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>133466</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>275986</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.7935263272297811</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.8081615667728164</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8183724016424762</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>132140; 149733</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>125296; 139797</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>263156; 286800</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.8991805375453538</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9016956173075513</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.8919014828418362</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.883278764302051</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8765116922183627</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8799176315926709</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>146770</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>143730</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>290500</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8310101021551146</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8296513769288154</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8454131661865035</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>138085; 153978</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>136045; 150160</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>279108; 299444</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9266578123356033</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9157262831397515</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9070112789214065</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1684</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.8991603690392778</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9070932139624025</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9029182447506929</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>617565</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>560772</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1178336</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8751361066392803</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.8858254007329041</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.8884007327942175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>601064; 631556</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>547624; 572223</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1159390; 1197619</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.91953108098611</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9256149765172565</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9176935597628771</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman una fruta o un zumo natural todos los días (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>152</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>113249</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>112352</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>225601</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>107292</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>217581</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>118038</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>115295</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>231353</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>304</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>255</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>215026</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>171225</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>386249</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>207417</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>165055</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>375567</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>221430</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>175240</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>393775</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>187</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>191</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>142520</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>133466</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>275986</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>132140</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>125296</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>263156</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>149733</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>139797</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>286800</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>207</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>146770</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>143730</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>290500</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>138085</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>136045</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>279108</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>153978</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>150160</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>299444</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>853</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>831</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>617565</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>560772</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1178336</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>601064</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>547624</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1159390</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>631556</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>572223</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1197619</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>